--- a/pages/shp/uploads/05092700718820260511005646.xlsx
+++ b/pages/shp/uploads/05092700718820260511005646.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EXIM2\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EXIM\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{790EDF9F-BBBC-41D3-81B7-3A151C409B52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD7D7D87-889E-4604-9A2F-0D67E0BD431A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="867" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HEADER" sheetId="1" r:id="rId1"/>
@@ -45,6 +45,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>

--- a/pages/shp/uploads/05092700718820260511005646.xlsx
+++ b/pages/shp/uploads/05092700718820260511005646.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EXIM\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD7D7D87-889E-4604-9A2F-0D67E0BD431A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95424DC6-D3D3-48A6-8A39-85B60D58C913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
